--- a/fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx
+++ b/fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx
@@ -7271,26 +7271,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7489,26 +7489,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7610,26 +7610,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7731,26 +7731,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7852,26 +7852,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7973,26 +7973,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -41661,7 +41661,7 @@
         <v>32</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>33</v>

--- a/fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx
+++ b/fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx
@@ -41753,7 +41753,7 @@
         <v>65</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.421833385510356</v>
+        <v>0.445687059095763</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>33</v>
@@ -41776,7 +41776,7 @@
         <v>65</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.400741716234838</v>
+        <v>0.423402706140975</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>33</v>
@@ -41799,7 +41799,7 @@
         <v>65</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.37965004695932</v>
+        <v>0.401118353186187</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>33</v>
@@ -41822,7 +41822,7 @@
         <v>65</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.358558377683802</v>
+        <v>0.378834000231398</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>33</v>
@@ -46004,19 +46004,19 @@
       </c>
       <c r="C7" s="15" t="n">
         <f aca="false">inl_26</f>
-        <v>0.421833385510356</v>
+        <v>0.445687059095763</v>
       </c>
       <c r="D7" s="15" t="n">
         <f aca="false">inl_27</f>
-        <v>0.400741716234838</v>
+        <v>0.423402706140975</v>
       </c>
       <c r="E7" s="15" t="n">
         <f aca="false">inl_28</f>
-        <v>0.37965004695932</v>
+        <v>0.401118353186187</v>
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">inl_29</f>
-        <v>0.358558377683802</v>
+        <v>0.378834000231398</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>587</v>
@@ -46031,19 +46031,19 @@
       </c>
       <c r="C8" s="15" t="n">
         <f aca="false">C6+C7</f>
-        <v>0.464185517521965</v>
+        <v>0.488039191107372</v>
       </c>
       <c r="D8" s="15" t="n">
         <f aca="false">D6+D7</f>
-        <v>0.449446668048189</v>
+        <v>0.472107657954326</v>
       </c>
       <c r="E8" s="15" t="n">
         <f aca="false">E6+E7</f>
-        <v>0.432590211973832</v>
+        <v>0.454058518200699</v>
       </c>
       <c r="F8" s="15" t="n">
         <f aca="false">F6+F7</f>
-        <v>0.413616149298894</v>
+        <v>0.43389177184649</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>589</v>
@@ -46082,19 +46082,19 @@
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">C4+C5-C7*C4-C9</f>
-        <v>16.2427666805634</v>
+        <v>15.5330420807143</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">D4+D5-D7*D4-D9</f>
-        <v>31.8841673549714</v>
+        <v>30.6704285329909</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">E4+E5-E7*E4-E9</f>
-        <v>38.0597447223195</v>
+        <v>36.8147654417642</v>
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">F4+F5-F7*F4-F9</f>
-        <v>51.578308874115</v>
+        <v>50.0995103987306</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>592</v>
@@ -52692,15 +52692,15 @@
       </c>
       <c r="C16" s="15" t="n">
         <f aca="false">Units!C8</f>
-        <v>0.464185517521965</v>
+        <v>0.488039191107372</v>
       </c>
       <c r="E16" s="15" t="n">
         <f aca="false">Units!C8</f>
-        <v>0.464185517521965</v>
+        <v>0.488039191107372</v>
       </c>
       <c r="G16" s="15" t="n">
         <f aca="false">Units!C8</f>
-        <v>0.464185517521965</v>
+        <v>0.488039191107372</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>854</v>
@@ -52715,15 +52715,15 @@
       </c>
       <c r="C17" s="15" t="n">
         <f aca="false">Units!E8</f>
-        <v>0.432590211973832</v>
+        <v>0.454058518200699</v>
       </c>
       <c r="E17" s="15" t="n">
         <f aca="false">Units!E8</f>
-        <v>0.432590211973832</v>
+        <v>0.454058518200699</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">Units!E8</f>
-        <v>0.432590211973832</v>
+        <v>0.454058518200699</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>857</v>

--- a/fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx
+++ b/fabrinet/dist/20261026_Fabrinet模型_v0.1.2.xlsx
@@ -6977,26 +6977,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">innolight/dist/20261026_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中際旭創模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">innolight/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中際旭創個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
